--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EEA759-3283-48A7-81A2-C811A70C7C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -28,8 +34,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,13 +98,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +150,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -170,6 +184,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -204,9 +219,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -379,11 +395,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C65"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -394,356 +410,708 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>0.001200288</v>
+        <v>1.0447410000000001E-3</v>
       </c>
       <c r="B2">
-        <v>0.01246567</v>
+        <v>0.159683723</v>
       </c>
       <c r="C2">
-        <v>4262.791032148901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>3784.939086294416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>0.001497338</v>
+        <v>1.5030569999999999E-3</v>
       </c>
       <c r="B3">
-        <v>0.132287681</v>
+        <v>2.2894349999999998E-3</v>
       </c>
       <c r="C3">
-        <v>3816.305837563452</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>3771.964467005077</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>0.001858829</v>
+        <v>1.789601E-3</v>
       </c>
       <c r="B4">
-        <v>0.0020691</v>
+        <v>2.1764748E-2</v>
       </c>
       <c r="C4">
-        <v>3603.937817258884</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>3617.673011844332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>0.002013396</v>
+        <v>2.18046E-3</v>
       </c>
       <c r="B5">
-        <v>0.58600681</v>
+        <v>0.57079832399999997</v>
       </c>
       <c r="C5">
-        <v>3759.764382402708</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>4285.3329103214901</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>0.002674114</v>
+        <v>2.7729320000000001E-3</v>
       </c>
       <c r="B6">
-        <v>0.0254425</v>
+        <v>5.0343530000000001E-3</v>
       </c>
       <c r="C6">
-        <v>3754.785532994925</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>3870.4086294416252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>0.003086928</v>
+        <v>3.4769050000000002E-3</v>
       </c>
       <c r="B7">
-        <v>0.005842734</v>
+        <v>4.5569369999999998E-2</v>
       </c>
       <c r="C7">
-        <v>4332.846023688664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>3631.1751269035531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>0.003764926</v>
+        <v>4.3494049999999998E-3</v>
       </c>
       <c r="B8">
-        <v>0.28711551</v>
+        <v>1.1481333999999999E-2</v>
       </c>
       <c r="C8">
-        <v>3669.115905245347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>3864.1539763113369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>0.004977475</v>
+        <v>5.2354139999999999E-3</v>
       </c>
       <c r="B9">
-        <v>0.054831019</v>
+        <v>0.25281826899999998</v>
       </c>
       <c r="C9">
-        <v>3964.467851099831</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>4183.7745346869706</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>0.00644151</v>
+        <v>6.4556199999999996E-3</v>
       </c>
       <c r="B10">
-        <v>0.001249672</v>
+        <v>1.5042359999999999E-3</v>
       </c>
       <c r="C10">
-        <v>3967.243231810491</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>3786.9877326565152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>0.008071493000000001</v>
+        <v>7.6548379999999997E-3</v>
       </c>
       <c r="B11">
-        <v>0.100039205</v>
+        <v>0.38417770800000001</v>
       </c>
       <c r="C11">
-        <v>3932.994077834179</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>3626.1861252115059</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>0.010292209</v>
+        <v>9.6973860000000005E-3</v>
       </c>
       <c r="B12">
-        <v>0.008448173</v>
+        <v>7.6256213000000003E-2</v>
       </c>
       <c r="C12">
-        <v>3852.802876480542</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>3678.7652284263968</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>0.012057157</v>
+        <v>1.1894497E-2</v>
       </c>
       <c r="B13">
-        <v>0.810093979</v>
+        <v>5.9016980000000004E-3</v>
       </c>
       <c r="C13">
-        <v>3820.963620981388</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>3933.70600676819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>0.013826926</v>
+        <v>1.6188659000000001E-2</v>
       </c>
       <c r="B14">
-        <v>0.003709931</v>
+        <v>2.9689E-2</v>
       </c>
       <c r="C14">
-        <v>3693.917512690356</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>4295.9644670050766</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>0.018598445</v>
+        <v>2.0324828E-2</v>
       </c>
       <c r="B15">
-        <v>0.037669258</v>
+        <v>0.94246236500000002</v>
       </c>
       <c r="C15">
-        <v>3599.122250423012</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>3950.3071065989861</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>0.023438181</v>
+        <v>2.3245913E-2</v>
       </c>
       <c r="B16">
-        <v>0.235570958</v>
+        <v>2.8355989999999998E-3</v>
       </c>
       <c r="C16">
-        <v>4348.772842639595</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>4110.2694585448398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>0.028054832</v>
+        <v>2.7012950000000001E-2</v>
       </c>
       <c r="B17">
-        <v>0.002539301</v>
+        <v>6.7603828000000005E-2</v>
       </c>
       <c r="C17">
-        <v>4354.065143824027</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>4047.010575296109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>0.033296084</v>
+        <v>3.6150422000000001E-2</v>
       </c>
       <c r="B18">
-        <v>0.08464574800000001</v>
+        <v>9.5587980000000003E-3</v>
       </c>
       <c r="C18">
-        <v>4022.680203045686</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>3783.2322335025392</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>0.044002681</v>
+        <v>4.2605628999999999E-2</v>
       </c>
       <c r="B19">
-        <v>0.029292955</v>
+        <v>0.31662526800000002</v>
       </c>
       <c r="C19">
-        <v>4140.410744500846</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>3992.4543147208128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>0.052151409</v>
+        <v>5.2952310000000002E-2</v>
       </c>
       <c r="B20">
-        <v>0.016056401</v>
+        <v>3.4455050000000002E-3</v>
       </c>
       <c r="C20">
-        <v>3718.495769881557</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>4347.5198815566846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>0.06327408</v>
+        <v>6.3086988999999996E-2</v>
       </c>
       <c r="B21">
-        <v>0.5183742220000001</v>
+        <v>0.141467806</v>
       </c>
       <c r="C21">
-        <v>4452.884940778342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>4467.3494077834184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>0.07783224900000001</v>
+        <v>8.1719082999999998E-2</v>
       </c>
       <c r="B22">
-        <v>0.001097566</v>
+        <v>1.8188362E-2</v>
       </c>
       <c r="C22">
-        <v>4175.068527918782</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>3464.9517766497461</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>0.097710587</v>
+        <v>0.11033149</v>
       </c>
       <c r="B23">
-        <v>0.211593646</v>
+        <v>1.0873090000000001E-3</v>
       </c>
       <c r="C23">
-        <v>4194.973773265652</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>5473.2643824027073</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>0.136451165</v>
+        <v>0.13598734400000001</v>
       </c>
       <c r="B24">
-        <v>0.040931093</v>
+        <v>0.76118231999999997</v>
       </c>
       <c r="C24">
-        <v>4225.11421319797</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>4347.5985617597307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>0.152879814</v>
+        <v>0.17578461500000001</v>
       </c>
       <c r="B25">
-        <v>0.004745768</v>
+        <v>5.6172774000000002E-2</v>
       </c>
       <c r="C25">
-        <v>4604.077834179358</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>4264.7914551607446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>0.192038208</v>
+        <v>0.20160655599999999</v>
       </c>
       <c r="B26">
-        <v>0.357504372</v>
+        <v>1.4644999000000001E-2</v>
       </c>
       <c r="C26">
-        <v>4645.424703891709</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>3526.3206429780039</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>0.233173154</v>
+        <v>0.265689966</v>
       </c>
       <c r="B27">
-        <v>0.020254295</v>
+        <v>3.6664359999999999E-3</v>
       </c>
       <c r="C27">
-        <v>3961.366328257191</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>7717.1362098138752</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>0.294162442</v>
+        <v>0.29276129499999998</v>
       </c>
       <c r="B28">
-        <v>0.003476933</v>
+        <v>0.21389501499999999</v>
       </c>
       <c r="C28">
-        <v>3806.824027072758</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>4390.7868020304568</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>0.362151881</v>
+        <v>0.41161421599999998</v>
       </c>
       <c r="B29">
-        <v>0.148571812</v>
+        <v>0.11442783500000001</v>
       </c>
       <c r="C29">
-        <v>4062.518612521151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>4094.1133671742809</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>0.512767952</v>
+        <v>0.456044008</v>
       </c>
       <c r="B30">
-        <v>0.001653693</v>
+        <v>7.0786249999999998E-3</v>
       </c>
       <c r="C30">
-        <v>3771.619289340102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>6341.7529610829106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>0.590904106</v>
+        <v>0.52990120200000002</v>
       </c>
       <c r="B31">
-        <v>0.757215055</v>
+        <v>3.6510218999999997E-2</v>
       </c>
       <c r="C31">
-        <v>3825.054991539764</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>3529.2546531302892</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>0.653502209</v>
+        <v>0.69212307699999998</v>
       </c>
       <c r="B32">
-        <v>0.009706993000000001</v>
+        <v>1.7836849999999999E-3</v>
       </c>
       <c r="C32">
-        <v>4003.847715736041</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>6355.9877326565156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>0.97027319</v>
+        <v>0.87460116300000001</v>
       </c>
       <c r="B33">
-        <v>0.061840059</v>
+        <v>0.50829114799999997</v>
       </c>
       <c r="C33">
-        <v>5001.218274111675</v>
+        <v>9987.7038917089685</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1.0001579999999999E-3</v>
+      </c>
+      <c r="B34">
+        <v>0.245258064</v>
+      </c>
+      <c r="C34">
+        <v>3378.957275803723</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1.004628E-3</v>
+      </c>
+      <c r="B35">
+        <v>0.97048507699999997</v>
+      </c>
+      <c r="C35">
+        <v>2974.3430626057539</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1.0193470000000001E-3</v>
+      </c>
+      <c r="B36">
+        <v>0.78367797900000002</v>
+      </c>
+      <c r="C36">
+        <v>6625.0401861252112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1.5636599999999999E-3</v>
+      </c>
+      <c r="B37">
+        <v>6.1181459000000001E-2</v>
+      </c>
+      <c r="C37">
+        <v>2839.6446700507622</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.7473079999999999E-3</v>
+      </c>
+      <c r="B38">
+        <v>9.2703667000000003E-2</v>
+      </c>
+      <c r="C38">
+        <v>2709.170050761421</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>2.104912E-3</v>
+      </c>
+      <c r="B39">
+        <v>4.2864859999999999E-3</v>
+      </c>
+      <c r="C39">
+        <v>2908.988155668359</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>2.2459260000000001E-3</v>
+      </c>
+      <c r="B40">
+        <v>1.0517713E-2</v>
+      </c>
+      <c r="C40">
+        <v>3859.0228426395938</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>3.2166870000000002E-3</v>
+      </c>
+      <c r="B41">
+        <v>1.767408E-3</v>
+      </c>
+      <c r="C41">
+        <v>3238.124788494079</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>3.5851059999999998E-3</v>
+      </c>
+      <c r="B42">
+        <v>5.0347209999999998E-3</v>
+      </c>
+      <c r="C42">
+        <v>8409.4606598984774</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>5.1209619999999997E-3</v>
+      </c>
+      <c r="B43">
+        <v>1.4271806E-2</v>
+      </c>
+      <c r="C43">
+        <v>2841.5444162436552</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1.0070803999999999E-2</v>
+      </c>
+      <c r="B44">
+        <v>5.1669189999999997E-2</v>
+      </c>
+      <c r="C44">
+        <v>3060.5647208121832</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1.9011876E-2</v>
+      </c>
+      <c r="B45">
+        <v>1E-3</v>
+      </c>
+      <c r="C45">
+        <v>3273.3832487309651</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>2.1881563E-2</v>
+      </c>
+      <c r="B46">
+        <v>1.3172730000000001E-3</v>
+      </c>
+      <c r="C46">
+        <v>8139.0224196277486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>2.8605589000000001E-2</v>
+      </c>
+      <c r="B47">
+        <v>1.0404940000000001E-3</v>
+      </c>
+      <c r="C47">
+        <v>7864.8862098138743</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>9.2537860999999999E-2</v>
+      </c>
+      <c r="B48">
+        <v>3.4197587000000002E-2</v>
+      </c>
+      <c r="C48">
+        <v>7701.1586294416238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>0.10055415700000001</v>
+      </c>
+      <c r="B49">
+        <v>0.126265341</v>
+      </c>
+      <c r="C49">
+        <v>3506.1434010152279</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>0.125746151</v>
+      </c>
+      <c r="B50">
+        <v>1.0074260000000001E-3</v>
+      </c>
+      <c r="C50">
+        <v>2970.8637901861262</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>0.12804692200000001</v>
+      </c>
+      <c r="B51">
+        <v>8.4266181999999995E-2</v>
+      </c>
+      <c r="C51">
+        <v>6798.6501692047386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>0.146068174</v>
+      </c>
+      <c r="B52">
+        <v>3.8091570000000001E-3</v>
+      </c>
+      <c r="C52">
+        <v>3958.823604060914</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>0.14911117099999999</v>
+      </c>
+      <c r="B53">
+        <v>1.4878255E-2</v>
+      </c>
+      <c r="C53">
+        <v>3198.6721658206438</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>0.207784366</v>
+      </c>
+      <c r="B54">
+        <v>6.8467152000000003E-2</v>
+      </c>
+      <c r="C54">
+        <v>3316.2186971235201</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>0.38428427599999998</v>
+      </c>
+      <c r="B55">
+        <v>0.19717085200000001</v>
+      </c>
+      <c r="C55">
+        <v>7936.63663282572</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>0.55359703299999996</v>
+      </c>
+      <c r="B56">
+        <v>1.783686E-3</v>
+      </c>
+      <c r="C56">
+        <v>3489.3570219966159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>0.81803113400000005</v>
+      </c>
+      <c r="B57">
+        <v>0.71615553499999995</v>
+      </c>
+      <c r="C57">
+        <v>2572.3549069373939</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>0.98744092299999997</v>
+      </c>
+      <c r="B58">
+        <v>1.0031879999999999E-3</v>
+      </c>
+      <c r="C58">
+        <v>2929.896362098139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>0.99959403199999997</v>
+      </c>
+      <c r="B59">
+        <v>1.3359730000000001E-3</v>
+      </c>
+      <c r="C59">
+        <v>5429.5964467005078</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>0.999815589</v>
+      </c>
+      <c r="B60">
+        <v>1.436164E-3</v>
+      </c>
+      <c r="C60">
+        <v>3580.520304568528</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61">
+        <v>1.0106679999999999E-3</v>
+      </c>
+      <c r="C61">
+        <v>2713.473350253807</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62">
+        <v>0.45487215600000003</v>
+      </c>
+      <c r="C62">
+        <v>8643.9175126903538</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>0.55079194099999995</v>
+      </c>
+      <c r="C63">
+        <v>4312.1763959390873</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64">
+        <v>0.64675649999999996</v>
+      </c>
+      <c r="C64">
+        <v>2852.9674280879858</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65">
+        <v>0.81711242699999997</v>
+      </c>
+      <c r="C65">
+        <v>3314.187817258884</v>
       </c>
     </row>
   </sheetData>
